--- a/output/Data and Chart Outputs/us_petroleum_stocks_weekly.xlsx
+++ b/output/Data and Chart Outputs/us_petroleum_stocks_weekly.xlsx
@@ -165,7 +165,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Jet Fuel Storage - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Jet Fuel Storage - water year (Oct-Sep), data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -277,7 +278,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -435,7 +436,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Commercial Crude Oil Storage (excl. SPR) - calendar-year weeks, data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Commercial Crude Oil Storage (excl. SPR) - calendar-year weeks, data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -547,7 +549,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -622,7 +624,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
@@ -705,7 +707,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Crude Oil Storage incl. SPR - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Crude Oil Storage incl. SPR - water year (Oct-Sep), data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -817,7 +820,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -912,8 +915,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1050000"/>
-          <min val="700000"/>
+          <max val="1100000"/>
+          <min val="600000"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -938,7 +941,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="50000"/>
+        <majorUnit val="100000"/>
       </valAx>
       <spPr>
         <a:ln>
@@ -975,7 +978,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Crude Oil Storage incl. SPR - calendar-year weeks, data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Crude Oil Storage incl. SPR - calendar-year weeks, data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1087,7 +1091,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1162,7 +1166,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
@@ -1183,7 +1187,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="1200000"/>
-          <min val="700000"/>
+          <min val="600000"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1245,7 +1249,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Big Four Storage (Crude with SPR + Gasoline + Distillate + Jet Fuel) - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Big Four Storage (Crude with SPR + Gasoline + Distillate + Jet Fuel) - water year (Oct-Sep), data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1357,7 +1362,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1515,7 +1520,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Big Four Storage (Crude with SPR + Gasoline + Distillate + Jet Fuel) - calendar-year weeks, data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Big Four Storage (Crude with SPR + Gasoline + Distillate + Jet Fuel) - calendar-year weeks, data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1627,7 +1633,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1702,7 +1708,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
@@ -1785,7 +1791,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Jet Fuel Storage - calendar-year weeks, data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Jet Fuel Storage - calendar-year weeks, data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1897,7 +1904,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1972,7 +1979,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
@@ -2055,7 +2062,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Distillate Fuel Oil Storage - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Distillate Fuel Oil Storage - water year (Oct-Sep), data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2167,7 +2175,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2325,7 +2333,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Distillate Fuel Oil Storage - calendar-year weeks, data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Distillate Fuel Oil Storage - calendar-year weeks, data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2437,7 +2446,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2512,7 +2521,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
@@ -2595,7 +2604,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Motor Gasoline Storage - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Motor Gasoline Storage - water year (Oct-Sep), data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2707,7 +2717,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2865,7 +2875,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Motor Gasoline Storage - calendar-year weeks, data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Motor Gasoline Storage - calendar-year weeks, data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2977,7 +2988,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3052,7 +3063,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
@@ -3135,7 +3146,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Strategic Petroleum Reserve - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Strategic Petroleum Reserve - water year (Oct-Sep), data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3247,7 +3259,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3405,7 +3417,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Strategic Petroleum Reserve - calendar-year weeks, data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Strategic Petroleum Reserve - calendar-year weeks, data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3517,7 +3530,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3592,7 +3605,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:p>
             <a:pPr>
               <a:defRPr/>
@@ -3675,7 +3688,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>U.S. Commercial Crude Oil Storage (excl. SPR) - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>U.S. Commercial Crude Oil Storage (excl. SPR) - water year (Oct-Sep), data to 2026-10-16</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3787,7 +3801,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4917,6 +4931,9 @@
       <c r="E10" t="n">
         <v>425380</v>
       </c>
+      <c r="G10" t="n">
+        <v>415577</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5052,6 +5069,9 @@
       </c>
       <c r="E17" t="n">
         <v>424684</v>
+      </c>
+      <c r="G17" t="n">
+        <v>412517</v>
       </c>
     </row>
     <row r="18">
@@ -11982,7 +12002,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Wk 1</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12107,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Wk 5</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12212,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Wk 9</t>
         </is>
       </c>
     </row>
@@ -12297,7 +12317,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Wk 13</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12422,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Week 17</t>
+          <t>Wk 17</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12527,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Week 21</t>
+          <t>Wk 21</t>
         </is>
       </c>
     </row>
@@ -12612,7 +12632,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Week 25</t>
+          <t>Wk 25</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12737,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Week 29</t>
+          <t>Wk 29</t>
         </is>
       </c>
     </row>
@@ -12822,7 +12842,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Week 33</t>
+          <t>Wk 33</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12947,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Week 37</t>
+          <t>Wk 37</t>
         </is>
       </c>
     </row>
@@ -13027,9 +13047,12 @@
       <c r="F42" t="n">
         <v>423785</v>
       </c>
+      <c r="G42" t="n">
+        <v>415577</v>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Week 41</t>
+          <t>Wk 41</t>
         </is>
       </c>
     </row>
@@ -13054,6 +13077,9 @@
       <c r="F43" t="n">
         <v>422824</v>
       </c>
+      <c r="G43" t="n">
+        <v>412517</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13122,7 +13148,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Week 45</t>
+          <t>Wk 45</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13241,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Week 49</t>
+          <t>Wk 49</t>
         </is>
       </c>
     </row>
@@ -13532,6 +13558,9 @@
       <c r="E10" t="n">
         <v>937737.5</v>
       </c>
+      <c r="G10" t="n">
+        <v>698560</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13667,6 +13696,9 @@
       </c>
       <c r="E17" t="n">
         <v>936604</v>
+      </c>
+      <c r="G17" t="n">
+        <v>695200</v>
       </c>
     </row>
     <row r="18">
@@ -20597,7 +20629,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Wk 1</t>
         </is>
       </c>
     </row>
@@ -20702,7 +20734,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Wk 5</t>
         </is>
       </c>
     </row>
@@ -20807,7 +20839,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Wk 9</t>
         </is>
       </c>
     </row>
@@ -20912,7 +20944,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Wk 13</t>
         </is>
       </c>
     </row>
@@ -21017,7 +21049,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Week 17</t>
+          <t>Wk 17</t>
         </is>
       </c>
     </row>
@@ -21122,7 +21154,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Week 21</t>
+          <t>Wk 21</t>
         </is>
       </c>
     </row>
@@ -21227,7 +21259,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Week 25</t>
+          <t>Wk 25</t>
         </is>
       </c>
     </row>
@@ -21332,7 +21364,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Week 29</t>
+          <t>Wk 29</t>
         </is>
       </c>
     </row>
@@ -21437,7 +21469,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Week 33</t>
+          <t>Wk 33</t>
         </is>
       </c>
     </row>
@@ -21542,7 +21574,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Week 37</t>
+          <t>Wk 37</t>
         </is>
       </c>
     </row>
@@ -21642,9 +21674,12 @@
       <c r="F42" t="n">
         <v>831530</v>
       </c>
+      <c r="G42" t="n">
+        <v>698560</v>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Week 41</t>
+          <t>Wk 41</t>
         </is>
       </c>
     </row>
@@ -21669,6 +21704,9 @@
       <c r="F43" t="n">
         <v>831388</v>
       </c>
+      <c r="G43" t="n">
+        <v>695200</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -21737,7 +21775,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Week 45</t>
+          <t>Wk 45</t>
         </is>
       </c>
     </row>
@@ -21830,7 +21868,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Week 49</t>
+          <t>Wk 49</t>
         </is>
       </c>
     </row>
@@ -22147,6 +22185,9 @@
       <c r="E10" t="n">
         <v>1324783.5</v>
       </c>
+      <c r="G10" t="n">
+        <v>1052228</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22282,6 +22323,9 @@
       </c>
       <c r="E17" t="n">
         <v>1316252.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1047402</v>
       </c>
     </row>
     <row r="18">
@@ -29212,7 +29256,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Wk 1</t>
         </is>
       </c>
     </row>
@@ -29317,7 +29361,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Wk 5</t>
         </is>
       </c>
     </row>
@@ -29422,7 +29466,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Wk 9</t>
         </is>
       </c>
     </row>
@@ -29527,7 +29571,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Wk 13</t>
         </is>
       </c>
     </row>
@@ -29632,7 +29676,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Week 17</t>
+          <t>Wk 17</t>
         </is>
       </c>
     </row>
@@ -29737,7 +29781,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Week 21</t>
+          <t>Wk 21</t>
         </is>
       </c>
     </row>
@@ -29842,7 +29886,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Week 25</t>
+          <t>Wk 25</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29991,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Week 29</t>
+          <t>Wk 29</t>
         </is>
       </c>
     </row>
@@ -30052,7 +30096,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Week 33</t>
+          <t>Wk 33</t>
         </is>
       </c>
     </row>
@@ -30157,7 +30201,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Week 37</t>
+          <t>Wk 37</t>
         </is>
       </c>
     </row>
@@ -30257,9 +30301,12 @@
       <c r="F42" t="n">
         <v>1211800</v>
       </c>
+      <c r="G42" t="n">
+        <v>1052228</v>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Week 41</t>
+          <t>Wk 41</t>
         </is>
       </c>
     </row>
@@ -30284,6 +30331,9 @@
       <c r="F43" t="n">
         <v>1206547</v>
       </c>
+      <c r="G43" t="n">
+        <v>1047402</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -30352,7 +30402,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Week 45</t>
+          <t>Wk 45</t>
         </is>
       </c>
     </row>
@@ -30445,7 +30495,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Week 49</t>
+          <t>Wk 49</t>
         </is>
       </c>
     </row>
@@ -30527,7 +30577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H876"/>
+  <dimension ref="A1:H878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53320,6 +53370,58 @@
       </c>
       <c r="H876" t="n">
         <v>1059503</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B877" t="n">
+        <v>415577</v>
+      </c>
+      <c r="C877" t="n">
+        <v>282983</v>
+      </c>
+      <c r="D877" t="n">
+        <v>208262</v>
+      </c>
+      <c r="E877" t="n">
+        <v>102611</v>
+      </c>
+      <c r="F877" t="n">
+        <v>42795</v>
+      </c>
+      <c r="G877" t="n">
+        <v>698560</v>
+      </c>
+      <c r="H877" t="n">
+        <v>1052228</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B878" t="n">
+        <v>412517</v>
+      </c>
+      <c r="C878" t="n">
+        <v>282683</v>
+      </c>
+      <c r="D878" t="n">
+        <v>205310</v>
+      </c>
+      <c r="E878" t="n">
+        <v>104286</v>
+      </c>
+      <c r="F878" t="n">
+        <v>42606</v>
+      </c>
+      <c r="G878" t="n">
+        <v>695200</v>
+      </c>
+      <c r="H878" t="n">
+        <v>1047402</v>
       </c>
     </row>
   </sheetData>
@@ -53568,6 +53670,9 @@
       <c r="E10" t="n">
         <v>42911</v>
       </c>
+      <c r="G10" t="n">
+        <v>42795</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -53703,6 +53808,9 @@
       </c>
       <c r="E17" t="n">
         <v>41967</v>
+      </c>
+      <c r="G17" t="n">
+        <v>42606</v>
       </c>
     </row>
     <row r="18">
@@ -60633,7 +60741,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Wk 1</t>
         </is>
       </c>
     </row>
@@ -60738,7 +60846,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Wk 5</t>
         </is>
       </c>
     </row>
@@ -60843,7 +60951,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Wk 9</t>
         </is>
       </c>
     </row>
@@ -60948,7 +61056,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Wk 13</t>
         </is>
       </c>
     </row>
@@ -61053,7 +61161,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Week 17</t>
+          <t>Wk 17</t>
         </is>
       </c>
     </row>
@@ -61158,7 +61266,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Week 21</t>
+          <t>Wk 21</t>
         </is>
       </c>
     </row>
@@ -61263,7 +61371,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Week 25</t>
+          <t>Wk 25</t>
         </is>
       </c>
     </row>
@@ -61368,7 +61476,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Week 29</t>
+          <t>Wk 29</t>
         </is>
       </c>
     </row>
@@ -61473,7 +61581,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Week 33</t>
+          <t>Wk 33</t>
         </is>
       </c>
     </row>
@@ -61578,7 +61686,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Week 37</t>
+          <t>Wk 37</t>
         </is>
       </c>
     </row>
@@ -61678,9 +61786,12 @@
       <c r="F42" t="n">
         <v>44414</v>
       </c>
+      <c r="G42" t="n">
+        <v>42795</v>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Week 41</t>
+          <t>Wk 41</t>
         </is>
       </c>
     </row>
@@ -61705,6 +61816,9 @@
       <c r="F43" t="n">
         <v>42929</v>
       </c>
+      <c r="G43" t="n">
+        <v>42606</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -61773,7 +61887,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Week 45</t>
+          <t>Wk 45</t>
         </is>
       </c>
     </row>
@@ -61866,7 +61980,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Week 49</t>
+          <t>Wk 49</t>
         </is>
       </c>
     </row>
@@ -62183,6 +62297,9 @@
       <c r="E10" t="n">
         <v>123168.5</v>
       </c>
+      <c r="G10" t="n">
+        <v>102611</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -62318,6 +62435,9 @@
       </c>
       <c r="E17" t="n">
         <v>120472.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>104286</v>
       </c>
     </row>
     <row r="18">
@@ -69248,7 +69368,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Wk 1</t>
         </is>
       </c>
     </row>
@@ -69353,7 +69473,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Wk 5</t>
         </is>
       </c>
     </row>
@@ -69458,7 +69578,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Wk 9</t>
         </is>
       </c>
     </row>
@@ -69563,7 +69683,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Wk 13</t>
         </is>
       </c>
     </row>
@@ -69668,7 +69788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Week 17</t>
+          <t>Wk 17</t>
         </is>
       </c>
     </row>
@@ -69773,7 +69893,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Week 21</t>
+          <t>Wk 21</t>
         </is>
       </c>
     </row>
@@ -69878,7 +69998,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Week 25</t>
+          <t>Wk 25</t>
         </is>
       </c>
     </row>
@@ -69983,7 +70103,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Week 29</t>
+          <t>Wk 29</t>
         </is>
       </c>
     </row>
@@ -70088,7 +70208,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Week 33</t>
+          <t>Wk 33</t>
         </is>
       </c>
     </row>
@@ -70193,7 +70313,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Week 37</t>
+          <t>Wk 37</t>
         </is>
       </c>
     </row>
@@ -70293,9 +70413,12 @@
       <c r="F42" t="n">
         <v>117030</v>
       </c>
+      <c r="G42" t="n">
+        <v>102611</v>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Week 41</t>
+          <t>Wk 41</t>
         </is>
       </c>
     </row>
@@ -70320,6 +70443,9 @@
       <c r="F43" t="n">
         <v>115551</v>
       </c>
+      <c r="G43" t="n">
+        <v>104286</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -70388,7 +70514,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Week 45</t>
+          <t>Wk 45</t>
         </is>
       </c>
     </row>
@@ -70481,7 +70607,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Week 49</t>
+          <t>Wk 49</t>
         </is>
       </c>
     </row>
@@ -70798,6 +70924,9 @@
       <c r="E10" t="n">
         <v>220966.5</v>
       </c>
+      <c r="G10" t="n">
+        <v>208262</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -70933,6 +71062,9 @@
       </c>
       <c r="E17" t="n">
         <v>217209</v>
+      </c>
+      <c r="G17" t="n">
+        <v>205310</v>
       </c>
     </row>
     <row r="18">
@@ -77863,7 +77995,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Wk 1</t>
         </is>
       </c>
     </row>
@@ -77968,7 +78100,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Wk 5</t>
         </is>
       </c>
     </row>
@@ -78073,7 +78205,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Wk 9</t>
         </is>
       </c>
     </row>
@@ -78178,7 +78310,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Wk 13</t>
         </is>
       </c>
     </row>
@@ -78283,7 +78415,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Week 17</t>
+          <t>Wk 17</t>
         </is>
       </c>
     </row>
@@ -78388,7 +78520,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Week 21</t>
+          <t>Wk 21</t>
         </is>
       </c>
     </row>
@@ -78493,7 +78625,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Week 25</t>
+          <t>Wk 25</t>
         </is>
       </c>
     </row>
@@ -78598,7 +78730,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Week 29</t>
+          <t>Wk 29</t>
         </is>
       </c>
     </row>
@@ -78703,7 +78835,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Week 33</t>
+          <t>Wk 33</t>
         </is>
       </c>
     </row>
@@ -78808,7 +78940,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Week 37</t>
+          <t>Wk 37</t>
         </is>
       </c>
     </row>
@@ -78908,9 +79040,12 @@
       <c r="F42" t="n">
         <v>218826</v>
       </c>
+      <c r="G42" t="n">
+        <v>208262</v>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Week 41</t>
+          <t>Wk 41</t>
         </is>
       </c>
     </row>
@@ -78935,6 +79070,9 @@
       <c r="F43" t="n">
         <v>216679</v>
       </c>
+      <c r="G43" t="n">
+        <v>205310</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -79003,7 +79141,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Week 45</t>
+          <t>Wk 45</t>
         </is>
       </c>
     </row>
@@ -79096,7 +79234,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Week 49</t>
+          <t>Wk 49</t>
         </is>
       </c>
     </row>
@@ -79413,6 +79551,9 @@
       <c r="E10" t="n">
         <v>512357.5</v>
       </c>
+      <c r="G10" t="n">
+        <v>282983</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -79548,6 +79689,9 @@
       </c>
       <c r="E17" t="n">
         <v>511920</v>
+      </c>
+      <c r="G17" t="n">
+        <v>282683</v>
       </c>
     </row>
     <row r="18">
@@ -86478,7 +86622,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Week 1</t>
+          <t>Wk 1</t>
         </is>
       </c>
     </row>
@@ -86583,7 +86727,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Week 5</t>
+          <t>Wk 5</t>
         </is>
       </c>
     </row>
@@ -86688,7 +86832,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Week 9</t>
+          <t>Wk 9</t>
         </is>
       </c>
     </row>
@@ -86793,7 +86937,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Wk 13</t>
         </is>
       </c>
     </row>
@@ -86898,7 +87042,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Week 17</t>
+          <t>Wk 17</t>
         </is>
       </c>
     </row>
@@ -87003,7 +87147,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Week 21</t>
+          <t>Wk 21</t>
         </is>
       </c>
     </row>
@@ -87108,7 +87252,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Week 25</t>
+          <t>Wk 25</t>
         </is>
       </c>
     </row>
@@ -87213,7 +87357,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Week 29</t>
+          <t>Wk 29</t>
         </is>
       </c>
     </row>
@@ -87318,7 +87462,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Week 33</t>
+          <t>Wk 33</t>
         </is>
       </c>
     </row>
@@ -87423,7 +87567,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Week 37</t>
+          <t>Wk 37</t>
         </is>
       </c>
     </row>
@@ -87523,9 +87667,12 @@
       <c r="F42" t="n">
         <v>407745</v>
       </c>
+      <c r="G42" t="n">
+        <v>282983</v>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Week 41</t>
+          <t>Wk 41</t>
         </is>
       </c>
     </row>
@@ -87550,6 +87697,9 @@
       <c r="F43" t="n">
         <v>408564</v>
       </c>
+      <c r="G43" t="n">
+        <v>282683</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -87618,7 +87768,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Week 45</t>
+          <t>Wk 45</t>
         </is>
       </c>
     </row>
@@ -87711,7 +87861,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Week 49</t>
+          <t>Wk 49</t>
         </is>
       </c>
     </row>
